--- a/fix/328-insee-code-valueset/ig/CodeSystem-fr-core-cs-type-organisation.xlsx
+++ b/fix/328-insee-code-valueset/ig/CodeSystem-fr-core-cs-type-organisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:22:22+00:00</t>
+    <t>2026-07-27T07:26:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
